--- a/Result/profitability/6169.xlsx
+++ b/Result/profitability/6169.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.15</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.59375</v>
+        <v>-0.64125</v>
       </c>
       <c r="N2" t="n">
-        <v>-30.69</v>
+        <v>-133.2775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5687500000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="N3" t="n">
-        <v>-26.31125</v>
+        <v>-127.50375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3412500000000001</v>
+        <v>-0.36375</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.02875</v>
+        <v>-126.34625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>3.84</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2062499999999999</v>
+        <v>0.2162499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-16.57625</v>
+        <v>-119.84875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>21.25</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9625</v>
+        <v>2.9525</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.89625</v>
+        <v>-115.89875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-5.62</v>
       </c>
       <c r="M7" t="n">
-        <v>2.34</v>
+        <v>2.30625</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.748750000000001</v>
+        <v>-110.5375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>4.73</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9875</v>
+        <v>2.9825</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8375000000000004</v>
+        <v>-29.56374999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>-0.96</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9525</v>
+        <v>2.952500000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>81.04875000000001</v>
+        <v>81.04875000000003</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6169</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-791.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-19704.21%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-137.0175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03999999999999992</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.0588235294117645</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-243.21</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4435144154494228</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-826.1800000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-23.87803468208093</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
